--- a/Projects/Datasets for Excel/Datasets for excel/employee_dataset.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/employee_dataset.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2698A4-B202-4B31-A56F-8499ECE2BDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15283" yWindow="0" windowWidth="10895" windowHeight="16397" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
